--- a/data/trans_dic/P22$concerEmp-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,29</t>
+          <t>0,8; 2,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,89</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,36</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,15</t>
+          <t>0,41; 1,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,41</t>
+          <t>0,04; 0,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,21</t>
+          <t>0,0; 0,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,35</t>
+          <t>1,82; 3,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,11</t>
+          <t>0,95; 2,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,01</t>
+          <t>0,21; 0,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,91</t>
+          <t>0,79; 2,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,83</t>
+          <t>0,18; 0,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,66</t>
+          <t>0,14; 0,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,85</t>
+          <t>0,29; 0,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,05</t>
+          <t>1,1; 1,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,26</t>
+          <t>0,58; 1,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,68</t>
+          <t>0,23; 0,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,24</t>
+          <t>0,62; 1,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,89</t>
+          <t>1,7; 4,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,37</t>
+          <t>0,67; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,18</t>
+          <t>0,57; 3,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,5</t>
+          <t>1,63; 4,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,77</t>
+          <t>1,06; 3,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,25</t>
+          <t>0,85; 3,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,24</t>
+          <t>0,38; 2,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,01</t>
+          <t>0,9; 2,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,84</t>
+          <t>1,81; 3,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,8</t>
+          <t>0,95; 2,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,31</t>
+          <t>0,75; 2,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,32</t>
+          <t>1,52; 3,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,8</t>
+          <t>1,77; 2,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,6</t>
+          <t>0,78; 1,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,95</t>
+          <t>0,33; 0,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,91</t>
+          <t>0,95; 1,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,86</t>
+          <t>0,34; 0,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,65</t>
+          <t>0,2; 0,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,59</t>
+          <t>0,2; 0,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,91</t>
+          <t>0,41; 0,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,68</t>
+          <t>1,11; 1,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,01</t>
+          <t>0,55; 0,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,66</t>
+          <t>0,31; 0,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,27</t>
+          <t>0,75; 1,26</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8229; 23548</t>
+          <t>8204; 24754</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>800; 8668</t>
+          <t>797; 7918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1898</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 5245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6629</t>
+          <t>0; 6125</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5646</t>
+          <t>0; 5372</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3572</t>
+          <t>0; 4272</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2035</t>
+          <t>0; 1823</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9542; 26938</t>
+          <t>9653; 26121</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1028; 9394</t>
+          <t>1027; 9662</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3743</t>
+          <t>0; 4431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5501</t>
+          <t>0; 7294</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31090; 56537</t>
+          <t>30690; 56731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17995; 41363</t>
+          <t>18581; 41741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4647; 20952</t>
+          <t>4430; 19908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16702; 43802</t>
+          <t>18026; 45970</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2305; 13182</t>
+          <t>2819; 14647</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>997; 9838</t>
+          <t>995; 9843</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2107; 13052</t>
+          <t>2844; 13209</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6373; 19036</t>
+          <t>6392; 18048</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37031; 67083</t>
+          <t>36016; 64150</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22342; 46734</t>
+          <t>21744; 45030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9548; 27609</t>
+          <t>9259; 26646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27698; 56256</t>
+          <t>27909; 58454</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10060; 26965</t>
+          <t>9380; 26647</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3049; 16203</t>
+          <t>3203; 17981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3621; 17378</t>
+          <t>3131; 16801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10242; 29074</t>
+          <t>10542; 30666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5487; 17981</t>
+          <t>5047; 18433</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3818; 14914</t>
+          <t>3888; 15946</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2031; 12315</t>
+          <t>2062; 12594</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6095; 19899</t>
+          <t>5967; 19140</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18196; 39489</t>
+          <t>18560; 39756</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8571; 26280</t>
+          <t>8921; 26313</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8421; 25324</t>
+          <t>8266; 24591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19771; 43353</t>
+          <t>19857; 41644</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58910; 91539</t>
+          <t>57796; 91154</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27025; 54811</t>
+          <t>26529; 52200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11208; 32046</t>
+          <t>10973; 32699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32089; 65956</t>
+          <t>32775; 65000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11173; 28937</t>
+          <t>11325; 29491</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7282; 22988</t>
+          <t>6993; 20250</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6724; 20869</t>
+          <t>6936; 21514</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15521; 33253</t>
+          <t>15042; 32347</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74200; 112004</t>
+          <t>73991; 113186</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38483; 70393</t>
+          <t>38135; 69072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21442; 45342</t>
+          <t>21325; 46563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53027; 90468</t>
+          <t>53224; 89372</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerEmp-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,41</t>
+          <t>0,81; 2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,81</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,24</t>
+          <t>0,0; 0,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,11</t>
+          <t>0,42; 1,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,42</t>
+          <t>0,04; 0,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,25</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,36</t>
+          <t>1,83; 3,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,13</t>
+          <t>0,97; 2,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,96</t>
+          <t>0,26; 0,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,01</t>
+          <t>0,87; 2,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,92</t>
+          <t>0,15; 0,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,56</t>
+          <t>0,06; 0,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,66</t>
+          <t>0,1; 0,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,81</t>
+          <t>0,33; 0,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,96</t>
+          <t>1,13; 1,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,21</t>
+          <t>0,59; 1,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,66</t>
+          <t>0,23; 0,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,29</t>
+          <t>0,69; 1,31</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,83</t>
+          <t>1,73; 4,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,74</t>
+          <t>0,64; 3,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,08</t>
+          <t>0,64; 3,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,74</t>
+          <t>1,76; 4,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,87</t>
+          <t>1,04; 3,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,48</t>
+          <t>0,87; 3,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,29</t>
+          <t>0,47; 2,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,9</t>
+          <t>0,93; 2,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,87</t>
+          <t>1,69; 3,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,8</t>
+          <t>0,95; 2,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,25</t>
+          <t>0,75; 2,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,19</t>
+          <t>1,56; 3,31</t>
         </is>
       </c>
     </row>
@@ -1084,34 +1084,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,79</t>
+          <t>1,76; 2,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,53</t>
+          <t>0,77; 1,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,97</t>
+          <t>0,33; 0,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,88</t>
+          <t>1,05; 1,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,87</t>
+          <t>0,32; 0,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,57</t>
+          <t>0,2; 0,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,61</t>
+          <t>0,2; 0,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,89</t>
+          <t>0,45; 0,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,7</t>
+          <t>1,1; 1,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,99</t>
+          <t>0,56; 0,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,67</t>
+          <t>0,32; 0,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,26</t>
+          <t>0,82; 1,34</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1429</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8204; 24754</t>
+          <t>8369; 23211</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>797; 7918</t>
+          <t>800; 7516</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1519,47 +1519,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5245</t>
+          <t>0; 5985</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6125</t>
+          <t>0; 6818</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5372</t>
+          <t>0; 4359</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4272</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1823</t>
+          <t>0; 2185</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9653; 26121</t>
+          <t>9758; 26158</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1027; 9662</t>
+          <t>982; 8842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4431</t>
+          <t>0; 3556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 7294</t>
+          <t>0; 5357</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39688</t>
+          <t>41353</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30690; 56731</t>
+          <t>30863; 57654</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18581; 41741</t>
+          <t>19031; 41305</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4430; 19908</t>
+          <t>5337; 19727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18026; 45970</t>
+          <t>19369; 44739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2819; 14647</t>
+          <t>2309; 13491</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>995; 9843</t>
+          <t>995; 9961</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2844; 13209</t>
+          <t>2044; 12747</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6392; 18048</t>
+          <t>7161; 18960</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36016; 64150</t>
+          <t>37046; 64768</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21744; 45030</t>
+          <t>21986; 46375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9259; 26646</t>
+          <t>9373; 28622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27909; 58454</t>
+          <t>30287; 57749</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>32679</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9380; 26647</t>
+          <t>9525; 26120</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3203; 17981</t>
+          <t>3077; 16587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3131; 16801</t>
+          <t>3504; 17334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10542; 30666</t>
+          <t>12502; 32940</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5047; 18433</t>
+          <t>4952; 17281</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3888; 15946</t>
+          <t>4000; 15477</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2062; 12594</t>
+          <t>2557; 12451</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5967; 19140</t>
+          <t>6858; 20503</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18560; 39756</t>
+          <t>17413; 37457</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8921; 26313</t>
+          <t>8965; 26772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8266; 24591</t>
+          <t>8232; 24485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19857; 41644</t>
+          <t>22593; 47884</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47582</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>75462</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57796; 91154</t>
+          <t>57515; 93141</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26529; 52200</t>
+          <t>26305; 54027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10973; 32699</t>
+          <t>11206; 30682</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32775; 65000</t>
+          <t>37109; 70059</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11325; 29491</t>
+          <t>10797; 28701</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6993; 20250</t>
+          <t>7265; 21656</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6936; 21514</t>
+          <t>6947; 20674</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15042; 32347</t>
+          <t>16817; 34106</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73991; 113186</t>
+          <t>73090; 113063</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38135; 69072</t>
+          <t>38921; 67710</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21325; 46563</t>
+          <t>22079; 47519</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53224; 89372</t>
+          <t>59468; 97033</t>
         </is>
       </c>
     </row>
